--- a/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6809.xlsx
+++ b/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6809.xlsx
@@ -1399,9 +1399,27 @@
       <c r="D15" t="n">
         <v>1.12</v>
       </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
       <c r="G15" t="n">
         <v>0.875</v>
       </c>
+      <c r="H15" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.875</v>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>6809-10-10-NWO-FG</t>
@@ -1414,12 +1432,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: M10@DRIVE, M5@DRIVE, M7@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6809-10-10 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: C4HEX@HEX, C3HEX@HEX, D1@BORE, D2@BORE] [BRENNAN-CAD 2026-10-21: M10@DRIVE, M5@DRIVE, M7@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6809-10-10 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6809-10-10 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6809-10-10-NWO-FG (PARTcommunity / CADENAS, M10@DRIVE=M, M5@DRIVE=M6, M7@DRIVE=M7, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6809-10-10 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6809-10-10-NWO-FG (PARTcommunity / CADENAS, M10@DRIVE=M, M5@DRIVE=M6, M7@DRIVE=M7, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6809-10-10-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: C4HEX@HEX=C1, C3HEX@HEX=C2, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1453,9 +1471,27 @@
       <c r="D16" t="n">
         <v>1.18</v>
       </c>
+      <c r="E16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.25</v>
+      </c>
       <c r="G16" t="n">
         <v>1.062</v>
       </c>
+      <c r="H16" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.0625</v>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>6809-12-12-NWO-FG</t>
@@ -1468,12 +1504,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: M10@DRIVE, M5@DRIVE, M7@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6809-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: C4HEX@HEX, C3HEX@HEX, D1@BORE, D2@BORE] [BRENNAN-CAD 2026-10-21: M10@DRIVE, M5@DRIVE, M7@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6809-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6809-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6809-12-12-NWO-FG (PARTcommunity / CADENAS, M10@DRIVE=M, M5@DRIVE=M6, M7@DRIVE=M7, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6809-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6809-12-12-NWO-FG (PARTcommunity / CADENAS, M10@DRIVE=M, M5@DRIVE=M6, M7@DRIVE=M7, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6809-12-12-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: C4HEX@HEX=C1, C3HEX@HEX=C2, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1507,9 +1543,27 @@
       <c r="D17" t="n">
         <v>1.4</v>
       </c>
+      <c r="E17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G17" t="n">
         <v>1.312</v>
       </c>
+      <c r="H17" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.3125</v>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>6809-16-16-NWO-FG</t>
@@ -1522,12 +1576,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: M10@DRIVE, M5@DRIVE, M7@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6809-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: C4HEX@HEX, C3HEX@HEX, D1@BORE, D2@BORE] [BRENNAN-CAD 2026-10-21: M10@DRIVE, M5@DRIVE, M7@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6809-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6809-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6809-16-16-NWO-FG (PARTcommunity / CADENAS, M10@DRIVE=M, M5@DRIVE=M6, M7@DRIVE=M7, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6809-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6809-16-16-NWO-FG (PARTcommunity / CADENAS, M10@DRIVE=M, M5@DRIVE=M6, M7@DRIVE=M7, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6809-16-16-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: C4HEX@HEX=C1, C3HEX@HEX=C2, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1561,9 +1615,27 @@
       <c r="D18" t="n">
         <v>1.61</v>
       </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.875</v>
+      </c>
       <c r="G18" t="n">
         <v>1.625</v>
       </c>
+      <c r="H18" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.625</v>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>6809-20-20-NWO-FG</t>
@@ -1576,12 +1648,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: M10@DRIVE, M5@DRIVE, M7@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6809-20-20 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: C4HEX@HEX, C3HEX@HEX, D1@BORE, D2@BORE] [BRENNAN-CAD 2026-10-21: M10@DRIVE, M5@DRIVE, M7@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6809-20-20 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6809-20-20 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6809-20-20-NWO-FG (PARTcommunity / CADENAS, M10@DRIVE=M, M5@DRIVE=M6, M7@DRIVE=M7, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6809-20-20 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6809-20-20-NWO-FG (PARTcommunity / CADENAS, M10@DRIVE=M, M5@DRIVE=M6, M7@DRIVE=M7, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6809-20-20-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: C4HEX@HEX=C1, C3HEX@HEX=C2, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1653,7 +1725,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1735,7 +1807,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1817,7 +1889,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
